--- a/Design Files/Relay-Driver-Board-v1.0/BOM/Client-BOM-Relay-Driver-Board-v1.0.xlsx
+++ b/Design Files/Relay-Driver-Board-v1.0/BOM/Client-BOM-Relay-Driver-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="216">
   <si>
     <t>#</t>
   </si>
@@ -652,6 +652,21 @@
   </si>
   <si>
     <t xml:space="preserve">16-SOIC </t>
+  </si>
+  <si>
+    <t>Perpheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>32V Blade fuse 7.5A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>028707.5PXCN</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1157,6 +1172,8 @@
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1240,7 +1257,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B44" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B45" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2548,6 +2565,37 @@
         <v>1</v>
       </c>
       <c r="K44" s="9"/>
+    </row>
+    <row r="45" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="11">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="J45" s="9">
+        <v>1</v>
+      </c>
+      <c r="K45" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
